--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54927502</v>
+        <v>54927500</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622738.1362252182</v>
+        <v>622738</v>
       </c>
       <c r="R2" t="n">
-        <v>6356783.592755895</v>
+        <v>6356784</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,21 +746,11 @@
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,6 +759,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>nyröjd skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,41 +776,40 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54927528</v>
+        <v>54927515</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622710.8740801797</v>
+        <v>622733</v>
       </c>
       <c r="R3" t="n">
-        <v>6356736.33181748</v>
+        <v>6356768</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +855,9 @@
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,19 +880,18 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>54927519</v>
       </c>
       <c r="B4" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622728.5437089476</v>
+        <v>622729</v>
       </c>
       <c r="R4" t="n">
-        <v>6356760.623410599</v>
+        <v>6356761</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,19 +959,9 @@
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,41 +984,40 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54927523</v>
+        <v>54927482</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622722.4443679119</v>
+        <v>622748</v>
       </c>
       <c r="R5" t="n">
-        <v>6356747.479508</v>
+        <v>6356814</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1063,9 @@
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,41 +1088,40 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54927517</v>
+        <v>54927523</v>
       </c>
       <c r="B6" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106812</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221423</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622728.5437089476</v>
+        <v>622722</v>
       </c>
       <c r="R6" t="n">
-        <v>6356760.623410599</v>
+        <v>6356747</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,21 +1167,11 @@
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1234,11 +1180,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>nyröjd skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1251,19 +1192,18 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54927515</v>
+        <v>54927517</v>
       </c>
       <c r="B7" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>221423</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622733.1828762478</v>
+        <v>622729</v>
       </c>
       <c r="R7" t="n">
-        <v>6356768.323080093</v>
+        <v>6356761</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1331,21 +1271,11 @@
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1354,6 +1284,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>nyröjd skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,19 +1301,18 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54927500</v>
+        <v>54927502</v>
       </c>
       <c r="B8" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,21 +1320,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>174</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622738.1362252182</v>
+        <v>622738</v>
       </c>
       <c r="R8" t="n">
-        <v>6356783.592755895</v>
+        <v>6356784</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,21 +1380,11 @@
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-08-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1469,11 +1393,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>nyröjd skogsmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1486,7 +1405,215 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>54927528</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103402</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västeralvar, Öl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>622711</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6356736</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>54927491</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224416</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ljus solvända</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Västeralvar, Öl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>622748</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6356814</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Böda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2015-08-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson, Bengt Westman, Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44885-2025 artfynd.xlsx
+++ b/artfynd/A 44885-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -781,6 +786,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927500</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927515</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927482</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927523</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927517</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927528</t>
         </is>
       </c>
     </row>
@@ -1614,8 +1659,24 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54927491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>